--- a/Docs/Pensão Igor 25/Pensão Igor 2025.xlsx
+++ b/Docs/Pensão Igor 25/Pensão Igor 2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\R\RGitRep\Docs\Pensão Igor 25\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{860B7187-D7A4-48D5-B7E6-A1B6DEBCF2C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE5DF2A9-F947-4D0A-A629-52DB19B26E36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{2B53A937-1FE4-4DCD-BCCF-E9C5F5834D0B}"/>
+    <workbookView xWindow="3636" yWindow="1020" windowWidth="17280" windowHeight="8988" xr2:uid="{2B53A937-1FE4-4DCD-BCCF-E9C5F5834D0B}"/>
   </bookViews>
   <sheets>
     <sheet name="Principal" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
   <si>
     <t>Mês Pensão</t>
   </si>
@@ -60,6 +60,24 @@
   </si>
   <si>
     <t>Total pago em 2025</t>
+  </si>
+  <si>
+    <t>Pago em Maio</t>
+  </si>
+  <si>
+    <t>Pago em Junho</t>
+  </si>
+  <si>
+    <t>Pago em Julho</t>
+  </si>
+  <si>
+    <t>Pago em Agosto</t>
+  </si>
+  <si>
+    <t>Pago em Setembro</t>
+  </si>
+  <si>
+    <t>Pago em Outubro</t>
   </si>
 </sst>
 </file>
@@ -107,7 +125,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -130,17 +148,6 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -152,8 +159,8 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -556,43 +563,67 @@
       <c r="A6" s="1">
         <v>45809</v>
       </c>
-      <c r="B6" s="2"/>
-      <c r="C6" s="3"/>
+      <c r="B6" s="2">
+        <v>3918.45</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
         <v>45839</v>
       </c>
-      <c r="B7" s="2"/>
-      <c r="C7" s="3"/>
+      <c r="B7" s="2">
+        <v>3918.45</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
         <v>45870</v>
       </c>
-      <c r="B8" s="2"/>
-      <c r="C8" s="3"/>
+      <c r="B8" s="2">
+        <v>3918.45</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" s="1">
         <v>45901</v>
       </c>
-      <c r="B9" s="2"/>
-      <c r="C9" s="3"/>
+      <c r="B9" s="2">
+        <v>3918.45</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" s="1">
         <v>45931</v>
       </c>
-      <c r="B10" s="2"/>
-      <c r="C10" s="3"/>
+      <c r="B10" s="2">
+        <v>4152.6400000000003</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>12</v>
+      </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" s="1">
         <v>45962</v>
       </c>
-      <c r="B11" s="2"/>
-      <c r="C11" s="3"/>
+      <c r="B11" s="2">
+        <v>4152.6400000000003</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" s="1">
@@ -609,9 +640,10 @@
       <c r="C13" s="3"/>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A14" s="3"/>
       <c r="B14" s="5">
         <f>SUM(B2:B13)</f>
-        <v>15958.349999999999</v>
+        <v>39937.43</v>
       </c>
       <c r="C14" s="6" t="s">
         <v>7</v>

--- a/Docs/Pensão Igor 25/Pensão Igor 2025.xlsx
+++ b/Docs/Pensão Igor 25/Pensão Igor 2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\R\RGitRep\Docs\Pensão Igor 25\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE5DF2A9-F947-4D0A-A629-52DB19B26E36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1EBE2D86-48FD-448F-9735-CFA932372A76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3636" yWindow="1020" windowWidth="17280" windowHeight="8988" xr2:uid="{2B53A937-1FE4-4DCD-BCCF-E9C5F5834D0B}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{2B53A937-1FE4-4DCD-BCCF-E9C5F5834D0B}"/>
   </bookViews>
   <sheets>
     <sheet name="Principal" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
   <si>
     <t>Mês Pensão</t>
   </si>
@@ -78,6 +78,9 @@
   </si>
   <si>
     <t>Pago em Outubro</t>
+  </si>
+  <si>
+    <t>Pago em Novembro</t>
   </si>
 </sst>
 </file>
@@ -497,14 +500,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BA501A0A-8321-4752-AC22-ACA6407DFB74}">
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.44140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="56.109375" customWidth="1"/>
+    <col min="1" max="1" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="56.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -515,7 +518,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>45689</v>
       </c>
@@ -526,7 +529,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>45717</v>
       </c>
@@ -537,7 +540,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>45748</v>
       </c>
@@ -548,7 +551,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>45778</v>
       </c>
@@ -559,7 +562,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>45809</v>
       </c>
@@ -570,7 +573,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>45839</v>
       </c>
@@ -581,7 +584,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>45870</v>
       </c>
@@ -592,7 +595,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>45901</v>
       </c>
@@ -603,7 +606,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>45931</v>
       </c>
@@ -614,7 +617,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>45962</v>
       </c>
@@ -625,25 +628,29 @@
         <v>13</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <v>45992</v>
       </c>
-      <c r="B12" s="2"/>
-      <c r="C12" s="3"/>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B12" s="2">
+        <v>4152.6400000000003</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
         <v>46023</v>
       </c>
       <c r="B13" s="2"/>
       <c r="C13" s="3"/>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="3"/>
       <c r="B14" s="5">
         <f>SUM(B2:B13)</f>
-        <v>39937.43</v>
+        <v>44090.07</v>
       </c>
       <c r="C14" s="6" t="s">
         <v>7</v>

--- a/Docs/Pensão Igor 25/Pensão Igor 2025.xlsx
+++ b/Docs/Pensão Igor 25/Pensão Igor 2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\R\RGitRep\Docs\Pensão Igor 25\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1EBE2D86-48FD-448F-9735-CFA932372A76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{954E3772-07BA-489C-A670-AD1E3E07C67C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{2B53A937-1FE4-4DCD-BCCF-E9C5F5834D0B}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{2B53A937-1FE4-4DCD-BCCF-E9C5F5834D0B}"/>
   </bookViews>
   <sheets>
     <sheet name="Principal" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
   <si>
     <t>Mês Pensão</t>
   </si>
@@ -81,6 +81,9 @@
   </si>
   <si>
     <t>Pago em Novembro</t>
+  </si>
+  <si>
+    <t>Pago em Dezembro</t>
   </si>
 </sst>
 </file>
@@ -500,14 +503,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BA501A0A-8321-4752-AC22-ACA6407DFB74}">
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="1" max="1" width="10.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="56.140625" customWidth="1"/>
+    <col min="1" max="1" width="10.68359375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.41796875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="56.15625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -518,7 +521,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" s="1">
         <v>45689</v>
       </c>
@@ -529,7 +532,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="1">
         <v>45717</v>
       </c>
@@ -540,7 +543,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="1">
         <v>45748</v>
       </c>
@@ -551,7 +554,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="1">
         <v>45778</v>
       </c>
@@ -562,7 +565,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" s="1">
         <v>45809</v>
       </c>
@@ -573,7 +576,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" s="1">
         <v>45839</v>
       </c>
@@ -584,7 +587,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" s="1">
         <v>45870</v>
       </c>
@@ -595,7 +598,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" s="1">
         <v>45901</v>
       </c>
@@ -606,7 +609,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" s="1">
         <v>45931</v>
       </c>
@@ -617,7 +620,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" s="1">
         <v>45962</v>
       </c>
@@ -628,7 +631,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" s="1">
         <v>45992</v>
       </c>
@@ -639,18 +642,22 @@
         <v>14</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" s="1">
         <v>46023</v>
       </c>
-      <c r="B13" s="2"/>
-      <c r="C13" s="3"/>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B13" s="2">
+        <v>4152.6400000000003</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" s="3"/>
       <c r="B14" s="5">
         <f>SUM(B2:B13)</f>
-        <v>44090.07</v>
+        <v>48242.71</v>
       </c>
       <c r="C14" s="6" t="s">
         <v>7</v>
